--- a/tests/test_files/Account_test.xlsx
+++ b/tests/test_files/Account_test.xlsx
@@ -725,7 +725,7 @@
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>dcdc8696-243a-43d1-ad68-138b293638f0</t>
+          <t>00000000-0000-4000-8000-000000000001</t>
         </is>
       </c>
     </row>
@@ -779,7 +779,7 @@
       </c>
       <c r="L5" s="6" t="inlineStr">
         <is>
-          <t>dcdc8696-243a-43d1-ad68-138b293638f0</t>
+          <t>00000000-0000-4000-8000-000000000001</t>
         </is>
       </c>
     </row>
@@ -985,7 +985,7 @@
       </c>
       <c r="L9" s="6" t="inlineStr">
         <is>
-          <t>67e5da21-5ed6-4ab4-8a94-9f26ea3ed8f8</t>
+          <t>00000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="L10" s="6" t="inlineStr">
         <is>
-          <t>67e5da21-5ed6-4ab4-8a94-9f26ea3ed8f8</t>
+          <t>00000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
     </row>
@@ -1093,7 +1093,7 @@
       </c>
       <c r="L11" s="6" t="inlineStr">
         <is>
-          <t>67e5da21-5ed6-4ab4-8a94-9f26ea3ed8f8</t>
+          <t>00000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
     </row>
@@ -1147,7 +1147,7 @@
       </c>
       <c r="L12" s="6" t="inlineStr">
         <is>
-          <t>67e5da21-5ed6-4ab4-8a94-9f26ea3ed8f8</t>
+          <t>00000000-0000-4000-8000-000000000002</t>
         </is>
       </c>
     </row>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="L13" s="6" t="inlineStr">
         <is>
-          <t>17faed2a-e91d-4cc0-9a70-546bb34b5679</t>
+          <t>00000000-0000-4000-8000-000000000003</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1255,7 @@
       </c>
       <c r="L14" s="6" t="inlineStr">
         <is>
-          <t>17faed2a-e91d-4cc0-9a70-546bb34b5679</t>
+          <t>00000000-0000-4000-8000-000000000003</t>
         </is>
       </c>
     </row>
@@ -1309,7 +1309,7 @@
       </c>
       <c r="L15" s="6" t="inlineStr">
         <is>
-          <t>5101d9e3-7f9b-4305-a524-e32ca697706e</t>
+          <t>00000000-0000-4000-8000-000000000004</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="L16" s="6" t="inlineStr">
         <is>
-          <t>5101d9e3-7f9b-4305-a524-e32ca697706e</t>
+          <t>00000000-0000-4000-8000-000000000004</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="L36" s="6" t="inlineStr">
         <is>
-          <t>bc11492f-9bdd-4bf8-ba1d-291745a63b39</t>
+          <t>00000000-0000-4000-8000-000000000005</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="L37" s="6" t="inlineStr">
         <is>
-          <t>bc11492f-9bdd-4bf8-ba1d-291745a63b39</t>
+          <t>00000000-0000-4000-8000-000000000005</t>
         </is>
       </c>
     </row>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="L41" s="6" t="inlineStr">
         <is>
-          <t>d20a5679-e5b2-4046-9c86-6455dd2d0b60</t>
+          <t>00000000-0000-4000-8000-000000000006</t>
         </is>
       </c>
     </row>
@@ -2653,7 +2653,7 @@
       </c>
       <c r="L42" s="6" t="inlineStr">
         <is>
-          <t>d20a5679-e5b2-4046-9c86-6455dd2d0b60</t>
+          <t>00000000-0000-4000-8000-000000000006</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="L43" s="6" t="inlineStr">
         <is>
-          <t>d20a5679-e5b2-4046-9c86-6455dd2d0b60</t>
+          <t>00000000-0000-4000-8000-000000000006</t>
         </is>
       </c>
     </row>
@@ -2761,7 +2761,7 @@
       </c>
       <c r="L44" s="6" t="inlineStr">
         <is>
-          <t>d20a5679-e5b2-4046-9c86-6455dd2d0b60</t>
+          <t>00000000-0000-4000-8000-000000000006</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="L47" s="6" t="inlineStr">
         <is>
-          <t>e062f74a-0378-4bf0-844c-2992c3556d9b</t>
+          <t>00000000-0000-4000-8000-000000000007</t>
         </is>
       </c>
     </row>
@@ -2969,7 +2969,7 @@
       </c>
       <c r="L48" s="6" t="inlineStr">
         <is>
-          <t>e062f74a-0378-4bf0-844c-2992c3556d9b</t>
+          <t>00000000-0000-4000-8000-000000000007</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="L51" s="6" t="inlineStr">
         <is>
-          <t>b87ebb0e-732d-4182-ae71-2d62e0b634a8</t>
+          <t>00000000-0000-4000-8000-000000000008</t>
         </is>
       </c>
     </row>
@@ -3177,7 +3177,7 @@
       </c>
       <c r="L52" s="6" t="inlineStr">
         <is>
-          <t>b87ebb0e-732d-4182-ae71-2d62e0b634a8</t>
+          <t>00000000-0000-4000-8000-000000000008</t>
         </is>
       </c>
     </row>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="L53" s="6" t="inlineStr">
         <is>
-          <t>84492501-60e3-41c6-893c-c2ee3545849e</t>
+          <t>00000000-0000-4000-8000-000000000009</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="L54" s="6" t="inlineStr">
         <is>
-          <t>84492501-60e3-41c6-893c-c2ee3545849e</t>
+          <t>00000000-0000-4000-8000-000000000009</t>
         </is>
       </c>
     </row>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L55" s="6" t="inlineStr">
         <is>
-          <t>1d45e903-a25d-4093-8326-4c8315543015</t>
+          <t>00000000-0000-4000-8000-000000000010</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
       </c>
       <c r="L56" s="6" t="inlineStr">
         <is>
-          <t>1d45e903-a25d-4093-8326-4c8315543015</t>
+          <t>00000000-0000-4000-8000-000000000010</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="L57" s="6" t="inlineStr">
         <is>
-          <t>1d45e903-a25d-4093-8326-4c8315543015</t>
+          <t>00000000-0000-4000-8000-000000000010</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="L58" s="6" t="inlineStr">
         <is>
-          <t>1d45e903-a25d-4093-8326-4c8315543015</t>
+          <t>00000000-0000-4000-8000-000000000010</t>
         </is>
       </c>
     </row>
